--- a/tests/ITER_3D_APEC_evol_coils/input_template.xlsx
+++ b/tests/ITER_3D_APEC_evol_coils/input_template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="1"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="element_types"/>
@@ -187,13 +187,13 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -225,7 +225,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="10">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
@@ -233,10 +233,7 @@
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -245,13 +242,7 @@
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -260,7 +251,7 @@
     <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -568,127 +559,127 @@
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="3" t="s">
         <v>49</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="4">
+      <c r="A2" s="3">
         <v>31</v>
       </c>
-      <c r="B2" s="4">
-        <v>1</v>
-      </c>
-      <c r="C2" s="4">
-        <v>0</v>
-      </c>
-      <c r="D2" s="4">
-        <v>1</v>
-      </c>
-      <c r="E2" s="4">
-        <v>0</v>
-      </c>
-      <c r="F2" s="4">
-        <v>0</v>
-      </c>
-      <c r="G2" s="4">
+      <c r="B2" s="3">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3">
+        <v>0</v>
+      </c>
+      <c r="D2" s="3">
+        <v>1</v>
+      </c>
+      <c r="E2" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2" s="3">
+        <v>0</v>
+      </c>
+      <c r="G2" s="3">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="4">
+      <c r="A3" s="3">
         <v>33</v>
       </c>
-      <c r="B3" s="4">
-        <v>1</v>
-      </c>
-      <c r="C3" s="4">
+      <c r="B3" s="3">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3">
         <v>3</v>
       </c>
-      <c r="D3" s="4">
-        <v>1</v>
-      </c>
-      <c r="E3" s="4">
-        <v>0</v>
-      </c>
-      <c r="F3" s="4">
-        <v>0</v>
-      </c>
-      <c r="G3" s="4">
+      <c r="D3" s="3">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="4">
+      <c r="A4" s="3">
         <v>34</v>
       </c>
-      <c r="B4" s="4">
-        <v>1</v>
-      </c>
-      <c r="C4" s="4">
+      <c r="B4" s="3">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3">
         <v>4</v>
       </c>
-      <c r="D4" s="4">
-        <v>1</v>
-      </c>
-      <c r="E4" s="4">
-        <v>0</v>
-      </c>
-      <c r="F4" s="4">
-        <v>0</v>
-      </c>
-      <c r="G4" s="4">
+      <c r="D4" s="3">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="7">
+      <c r="A5" s="3">
         <v>35</v>
       </c>
-      <c r="B5" s="7">
-        <v>1</v>
-      </c>
-      <c r="C5" s="7">
+      <c r="B5" s="3">
+        <v>1</v>
+      </c>
+      <c r="C5" s="3">
         <v>6</v>
       </c>
-      <c r="D5" s="7">
-        <v>1</v>
-      </c>
-      <c r="E5" s="7">
-        <v>0</v>
-      </c>
-      <c r="F5" s="7">
-        <v>0</v>
-      </c>
-      <c r="G5" s="7">
+      <c r="D5" s="3">
+        <v>1</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3">
         <v>0</v>
       </c>
     </row>
@@ -705,12 +696,12 @@
   <dimension ref="A1:B25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="9" t="s">
         <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -718,7 +709,7 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="7">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -726,7 +717,7 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="7">
+      <c r="A3" s="3">
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -734,7 +725,7 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="7">
+      <c r="A4" s="3">
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -742,7 +733,7 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="7">
+      <c r="A5" s="3">
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -750,7 +741,7 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="7">
+      <c r="A6" s="3">
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -758,7 +749,7 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="7">
+      <c r="A7" s="3">
         <v>3</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -766,7 +757,7 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="7">
+      <c r="A8" s="3">
         <v>4</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -774,7 +765,7 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
-      <c r="A9" s="7">
+      <c r="A9" s="3">
         <v>4</v>
       </c>
       <c r="B9" s="1" t="s">
@@ -782,7 +773,7 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
-      <c r="A10" s="7">
+      <c r="A10" s="3">
         <v>5</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -790,7 +781,7 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
-      <c r="A11" s="7">
+      <c r="A11" s="3">
         <v>5</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -798,7 +789,7 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
-      <c r="A12" s="7">
+      <c r="A12" s="3">
         <v>6</v>
       </c>
       <c r="B12" s="1" t="s">
@@ -806,7 +797,7 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
-      <c r="A13" s="7">
+      <c r="A13" s="3">
         <v>6</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -814,7 +805,7 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
-      <c r="A14" s="7">
+      <c r="A14" s="3">
         <v>11</v>
       </c>
       <c r="B14" s="1" t="s">
@@ -822,7 +813,7 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
-      <c r="A15" s="7">
+      <c r="A15" s="3">
         <v>11</v>
       </c>
       <c r="B15" s="1" t="s">
@@ -830,7 +821,7 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
-      <c r="A16" s="7">
+      <c r="A16" s="3">
         <v>12</v>
       </c>
       <c r="B16" s="1" t="s">
@@ -838,7 +829,7 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
-      <c r="A17" s="7">
+      <c r="A17" s="3">
         <v>12</v>
       </c>
       <c r="B17" s="1" t="s">
@@ -846,7 +837,7 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
-      <c r="A18" s="7">
+      <c r="A18" s="3">
         <v>13</v>
       </c>
       <c r="B18" s="1" t="s">
@@ -854,7 +845,7 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
-      <c r="A19" s="7">
+      <c r="A19" s="3">
         <v>13</v>
       </c>
       <c r="B19" s="1" t="s">
@@ -862,7 +853,7 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
-      <c r="A20" s="7">
+      <c r="A20" s="3">
         <v>14</v>
       </c>
       <c r="B20" s="1" t="s">
@@ -870,7 +861,7 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
-      <c r="A21" s="7">
+      <c r="A21" s="3">
         <v>14</v>
       </c>
       <c r="B21" s="1" t="s">
@@ -878,7 +869,7 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
-      <c r="A22" s="7">
+      <c r="A22" s="3">
         <v>15</v>
       </c>
       <c r="B22" s="1" t="s">
@@ -886,7 +877,7 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
-      <c r="A23" s="7">
+      <c r="A23" s="3">
         <v>15</v>
       </c>
       <c r="B23" s="1" t="s">
@@ -894,7 +885,7 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
-      <c r="A24" s="7">
+      <c r="A24" s="3">
         <v>16</v>
       </c>
       <c r="B24" s="1" t="s">
@@ -902,7 +893,7 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
-      <c r="A25" s="7">
+      <c r="A25" s="3">
         <v>16</v>
       </c>
       <c r="B25" s="1" t="s">
@@ -922,29 +913,29 @@
   <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="3" t="s">
         <v>32</v>
       </c>
       <c r="E1" s="2" t="s">
@@ -956,109 +947,109 @@
       <c r="G1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="3" t="s">
         <v>38</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="4">
+      <c r="A2" s="3">
         <v>21</v>
       </c>
-      <c r="B2" s="4">
-        <v>1</v>
-      </c>
-      <c r="C2" s="4">
-        <v>1</v>
-      </c>
-      <c r="D2" s="4">
-        <v>1</v>
-      </c>
-      <c r="E2" s="4">
-        <v>1</v>
-      </c>
-      <c r="F2" s="4">
-        <v>1</v>
-      </c>
-      <c r="G2" s="4">
-        <v>1</v>
-      </c>
-      <c r="H2" s="4">
-        <v>0</v>
-      </c>
-      <c r="I2" s="4">
-        <v>0</v>
-      </c>
-      <c r="J2" s="4">
+      <c r="B2" s="3">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3">
+        <v>1</v>
+      </c>
+      <c r="E2" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2" s="3">
+        <v>1</v>
+      </c>
+      <c r="G2" s="3">
+        <v>1</v>
+      </c>
+      <c r="H2" s="3">
+        <v>0</v>
+      </c>
+      <c r="I2" s="3">
+        <v>0</v>
+      </c>
+      <c r="J2" s="3">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="4">
+      <c r="A3" s="3">
         <v>23</v>
       </c>
-      <c r="B3" s="4">
-        <v>1</v>
-      </c>
-      <c r="C3" s="4">
-        <v>1</v>
-      </c>
-      <c r="D3" s="4">
-        <v>1</v>
-      </c>
-      <c r="E3" s="4">
-        <v>1</v>
-      </c>
-      <c r="F3" s="4">
-        <v>1</v>
-      </c>
-      <c r="G3" s="4">
-        <v>1</v>
-      </c>
-      <c r="H3" s="4">
-        <v>0</v>
-      </c>
-      <c r="I3" s="4">
-        <v>0</v>
-      </c>
-      <c r="J3" s="4">
+      <c r="B3" s="3">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3">
+        <v>1</v>
+      </c>
+      <c r="F3" s="3">
+        <v>1</v>
+      </c>
+      <c r="G3" s="3">
+        <v>1</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0</v>
+      </c>
+      <c r="J3" s="3">
         <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="4">
+      <c r="A4" s="3">
         <v>24</v>
       </c>
-      <c r="B4" s="4">
-        <v>1</v>
-      </c>
-      <c r="C4" s="4">
-        <v>1</v>
-      </c>
-      <c r="D4" s="4">
-        <v>1</v>
-      </c>
-      <c r="E4" s="3">
+      <c r="B4" s="3">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2">
         <v>8e-7</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="2">
         <v>8e-7</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="2">
         <v>8e-7</v>
       </c>
-      <c r="H4" s="4">
-        <v>0</v>
-      </c>
-      <c r="I4" s="4">
-        <v>0</v>
-      </c>
-      <c r="J4" s="4">
+      <c r="H4" s="3">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3">
+        <v>0</v>
+      </c>
+      <c r="J4" s="3">
         <v>0</v>
       </c>
     </row>
@@ -1075,955 +1066,955 @@
   <dimension ref="A1:T15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="17" max="17" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="18" max="18" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="19" max="19" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="20" max="20" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="17" max="17" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="18" max="18" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="19" max="19" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="20" max="20" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="7" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
+      <c r="A1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="N1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="O1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="P1" s="7" t="s">
+      <c r="P1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q1" s="7" t="s">
+      <c r="Q1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="R1" s="7" t="s">
+      <c r="R1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="S1" s="7" t="s">
+      <c r="S1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="T1" s="7" t="s">
+      <c r="T1" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="4">
-        <v>1</v>
-      </c>
-      <c r="B2" s="4">
-        <v>1</v>
-      </c>
-      <c r="C2" s="3">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2">
         <v>0.9437519</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="3">
         <v>249</v>
       </c>
-      <c r="E2" s="9">
+      <c r="E2" s="6">
         <v>23.3632862025091</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="2">
         <v>3.94</v>
       </c>
-      <c r="G2" s="4">
-        <v>0</v>
-      </c>
-      <c r="H2" s="4">
-        <v>1</v>
-      </c>
-      <c r="I2" s="4">
-        <v>0</v>
-      </c>
-      <c r="J2" s="3">
+      <c r="G2" s="3">
+        <v>0</v>
+      </c>
+      <c r="H2" s="3">
+        <v>1</v>
+      </c>
+      <c r="I2" s="3">
+        <v>0</v>
+      </c>
+      <c r="J2" s="2">
         <v>0.0162797144</v>
       </c>
-      <c r="K2" s="4">
+      <c r="K2" s="3">
         <v>180</v>
       </c>
-      <c r="L2" s="4">
-        <v>0</v>
-      </c>
-      <c r="M2" s="4">
-        <v>0</v>
-      </c>
-      <c r="N2" s="4">
-        <v>0</v>
-      </c>
-      <c r="O2" s="4">
-        <v>0</v>
-      </c>
-      <c r="P2" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="4">
-        <v>0</v>
-      </c>
-      <c r="R2" s="4">
-        <v>0</v>
-      </c>
-      <c r="S2" s="4">
-        <v>0</v>
-      </c>
-      <c r="T2" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="4">
+      <c r="L2" s="3">
+        <v>0</v>
+      </c>
+      <c r="M2" s="3">
+        <v>0</v>
+      </c>
+      <c r="N2" s="3">
+        <v>0</v>
+      </c>
+      <c r="O2" s="3">
+        <v>0</v>
+      </c>
+      <c r="P2" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="3">
+        <v>0</v>
+      </c>
+      <c r="R2" s="3">
+        <v>0</v>
+      </c>
+      <c r="S2" s="3">
+        <v>0</v>
+      </c>
+      <c r="T2" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
+      <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="B3" s="4">
-        <v>1</v>
-      </c>
-      <c r="C3" s="3">
+      <c r="B3" s="3">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2">
         <v>0.41453946</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="3">
         <v>116</v>
       </c>
-      <c r="E3" s="9">
+      <c r="E3" s="6">
         <v>21.592368145397543</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="2">
         <v>8.29</v>
       </c>
-      <c r="G3" s="4">
-        <v>0</v>
-      </c>
-      <c r="H3" s="4">
-        <v>1</v>
-      </c>
-      <c r="I3" s="4">
-        <v>0</v>
-      </c>
-      <c r="J3" s="3">
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3">
+        <v>1</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0</v>
+      </c>
+      <c r="J3" s="2">
         <v>0.01688462455</v>
       </c>
-      <c r="K3" s="4">
+      <c r="K3" s="3">
         <v>180</v>
       </c>
-      <c r="L3" s="4">
-        <v>0</v>
-      </c>
-      <c r="M3" s="4">
-        <v>0</v>
-      </c>
-      <c r="N3" s="4">
-        <v>0</v>
-      </c>
-      <c r="O3" s="4">
-        <v>0</v>
-      </c>
-      <c r="P3" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="4">
-        <v>0</v>
-      </c>
-      <c r="R3" s="4">
-        <v>0</v>
-      </c>
-      <c r="S3" s="4">
-        <v>0</v>
-      </c>
-      <c r="T3" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="4">
+      <c r="L3" s="3">
+        <v>0</v>
+      </c>
+      <c r="M3" s="3">
+        <v>0</v>
+      </c>
+      <c r="N3" s="3">
+        <v>0</v>
+      </c>
+      <c r="O3" s="3">
+        <v>0</v>
+      </c>
+      <c r="P3" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="3">
+        <v>0</v>
+      </c>
+      <c r="R3" s="3">
+        <v>0</v>
+      </c>
+      <c r="S3" s="3">
+        <v>0</v>
+      </c>
+      <c r="T3" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
+      <c r="A4" s="3">
         <v>3</v>
       </c>
-      <c r="B4" s="4">
-        <v>1</v>
-      </c>
-      <c r="C4" s="3">
+      <c r="B4" s="3">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2">
         <v>0.66413094</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="3">
         <v>186</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E4" s="6">
         <v>50.0742931710164</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="3">
         <v>12</v>
       </c>
-      <c r="G4" s="4">
-        <v>0</v>
-      </c>
-      <c r="H4" s="4">
-        <v>1</v>
-      </c>
-      <c r="I4" s="4">
-        <v>0</v>
-      </c>
-      <c r="J4" s="3">
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3">
+        <v>1</v>
+      </c>
+      <c r="I4" s="3">
+        <v>0</v>
+      </c>
+      <c r="J4" s="2">
         <v>0.03926740844</v>
       </c>
-      <c r="K4" s="4">
+      <c r="K4" s="3">
         <v>180</v>
       </c>
-      <c r="L4" s="4">
-        <v>0</v>
-      </c>
-      <c r="M4" s="4">
-        <v>0</v>
-      </c>
-      <c r="N4" s="4">
-        <v>0</v>
-      </c>
-      <c r="O4" s="4">
-        <v>0</v>
-      </c>
-      <c r="P4" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="4">
-        <v>0</v>
-      </c>
-      <c r="R4" s="4">
-        <v>0</v>
-      </c>
-      <c r="S4" s="4">
-        <v>0</v>
-      </c>
-      <c r="T4" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="4">
+      <c r="L4" s="3">
+        <v>0</v>
+      </c>
+      <c r="M4" s="3">
+        <v>0</v>
+      </c>
+      <c r="N4" s="3">
+        <v>0</v>
+      </c>
+      <c r="O4" s="3">
+        <v>0</v>
+      </c>
+      <c r="P4" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="3">
+        <v>0</v>
+      </c>
+      <c r="R4" s="3">
+        <v>0</v>
+      </c>
+      <c r="S4" s="3">
+        <v>0</v>
+      </c>
+      <c r="T4" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
+      <c r="A5" s="3">
         <v>4</v>
       </c>
-      <c r="B5" s="4">
-        <v>1</v>
-      </c>
-      <c r="C5" s="3">
+      <c r="B5" s="3">
+        <v>1</v>
+      </c>
+      <c r="C5" s="2">
         <v>0.60871516</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="3">
         <v>170</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="6">
         <v>45.89604179483366</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="3">
         <v>12</v>
       </c>
-      <c r="G5" s="4">
-        <v>0</v>
-      </c>
-      <c r="H5" s="4">
-        <v>1</v>
-      </c>
-      <c r="I5" s="4">
-        <v>0</v>
-      </c>
-      <c r="J5" s="3">
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3">
+        <v>1</v>
+      </c>
+      <c r="I5" s="3">
+        <v>0</v>
+      </c>
+      <c r="J5" s="2">
         <v>0.0356938854</v>
       </c>
-      <c r="K5" s="4">
+      <c r="K5" s="3">
         <v>180</v>
       </c>
-      <c r="L5" s="4">
-        <v>0</v>
-      </c>
-      <c r="M5" s="4">
-        <v>0</v>
-      </c>
-      <c r="N5" s="4">
-        <v>0</v>
-      </c>
-      <c r="O5" s="4">
-        <v>0</v>
-      </c>
-      <c r="P5" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="4">
-        <v>0</v>
-      </c>
-      <c r="R5" s="4">
-        <v>0</v>
-      </c>
-      <c r="S5" s="4">
-        <v>0</v>
-      </c>
-      <c r="T5" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="4">
+      <c r="L5" s="3">
+        <v>0</v>
+      </c>
+      <c r="M5" s="3">
+        <v>0</v>
+      </c>
+      <c r="N5" s="3">
+        <v>0</v>
+      </c>
+      <c r="O5" s="3">
+        <v>0</v>
+      </c>
+      <c r="P5" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="3">
+        <v>0</v>
+      </c>
+      <c r="R5" s="3">
+        <v>0</v>
+      </c>
+      <c r="S5" s="3">
+        <v>0</v>
+      </c>
+      <c r="T5" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
+      <c r="A6" s="3">
         <v>5</v>
       </c>
-      <c r="B6" s="4">
-        <v>1</v>
-      </c>
-      <c r="C6" s="3">
+      <c r="B6" s="3">
+        <v>1</v>
+      </c>
+      <c r="C6" s="2">
         <v>0.7749625</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="3">
         <v>217</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="6">
         <v>40.85286481643119</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="2">
         <v>8.39</v>
       </c>
-      <c r="G6" s="4">
-        <v>0</v>
-      </c>
-      <c r="H6" s="4">
-        <v>1</v>
-      </c>
-      <c r="I6" s="4">
-        <v>0</v>
-      </c>
-      <c r="J6" s="3">
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3">
+        <v>1</v>
+      </c>
+      <c r="I6" s="3">
+        <v>0</v>
+      </c>
+      <c r="J6" s="2">
         <v>0.03198199512</v>
       </c>
-      <c r="K6" s="4">
+      <c r="K6" s="3">
         <v>180</v>
       </c>
-      <c r="L6" s="4">
-        <v>0</v>
-      </c>
-      <c r="M6" s="4">
-        <v>0</v>
-      </c>
-      <c r="N6" s="4">
-        <v>0</v>
-      </c>
-      <c r="O6" s="4">
-        <v>0</v>
-      </c>
-      <c r="P6" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="4">
-        <v>0</v>
-      </c>
-      <c r="R6" s="4">
-        <v>0</v>
-      </c>
-      <c r="S6" s="4">
-        <v>0</v>
-      </c>
-      <c r="T6" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="4">
+      <c r="L6" s="3">
+        <v>0</v>
+      </c>
+      <c r="M6" s="3">
+        <v>0</v>
+      </c>
+      <c r="N6" s="3">
+        <v>0</v>
+      </c>
+      <c r="O6" s="3">
+        <v>0</v>
+      </c>
+      <c r="P6" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="3">
+        <v>0</v>
+      </c>
+      <c r="R6" s="3">
+        <v>0</v>
+      </c>
+      <c r="S6" s="3">
+        <v>0</v>
+      </c>
+      <c r="T6" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
+      <c r="A7" s="3">
         <v>6</v>
       </c>
-      <c r="B7" s="4">
-        <v>1</v>
-      </c>
-      <c r="C7" s="3">
+      <c r="B7" s="3">
+        <v>1</v>
+      </c>
+      <c r="C7" s="2">
         <v>1.7265925</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="3">
         <v>460</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="6">
         <v>46.97400771701641</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="2">
         <v>4.33</v>
       </c>
-      <c r="G7" s="4">
-        <v>0</v>
-      </c>
-      <c r="H7" s="4">
-        <v>1</v>
-      </c>
-      <c r="I7" s="4">
-        <v>0</v>
-      </c>
-      <c r="J7" s="3">
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3">
+        <v>1</v>
+      </c>
+      <c r="I7" s="3">
+        <v>0</v>
+      </c>
+      <c r="J7" s="2">
         <v>0.03318021032</v>
       </c>
-      <c r="K7" s="4">
+      <c r="K7" s="3">
         <v>180</v>
       </c>
-      <c r="L7" s="4">
-        <v>0</v>
-      </c>
-      <c r="M7" s="4">
-        <v>0</v>
-      </c>
-      <c r="N7" s="4">
-        <v>0</v>
-      </c>
-      <c r="O7" s="4">
-        <v>0</v>
-      </c>
-      <c r="P7" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="4">
-        <v>0</v>
-      </c>
-      <c r="R7" s="4">
-        <v>0</v>
-      </c>
-      <c r="S7" s="4">
-        <v>0</v>
-      </c>
-      <c r="T7" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="4">
+      <c r="L7" s="3">
+        <v>0</v>
+      </c>
+      <c r="M7" s="3">
+        <v>0</v>
+      </c>
+      <c r="N7" s="3">
+        <v>0</v>
+      </c>
+      <c r="O7" s="3">
+        <v>0</v>
+      </c>
+      <c r="P7" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="3">
+        <v>0</v>
+      </c>
+      <c r="R7" s="3">
+        <v>0</v>
+      </c>
+      <c r="S7" s="3">
+        <v>0</v>
+      </c>
+      <c r="T7" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
+      <c r="A8" s="3">
         <v>10</v>
       </c>
-      <c r="B8" s="4">
-        <v>1</v>
-      </c>
-      <c r="C8" s="3">
+      <c r="B8" s="3">
+        <v>1</v>
+      </c>
+      <c r="C8" s="2">
         <v>28.6027095</v>
       </c>
-      <c r="D8" s="4">
-        <v>0</v>
-      </c>
-      <c r="E8" s="9">
-        <v>0</v>
-      </c>
-      <c r="F8" s="4">
-        <v>0</v>
-      </c>
-      <c r="G8" s="4">
-        <v>0</v>
-      </c>
-      <c r="H8" s="4">
-        <v>0</v>
-      </c>
-      <c r="I8" s="4">
-        <v>0</v>
-      </c>
-      <c r="J8" s="4">
-        <v>0</v>
-      </c>
-      <c r="K8" s="4">
-        <v>0</v>
-      </c>
-      <c r="L8" s="4">
-        <v>0</v>
-      </c>
-      <c r="M8" s="4">
-        <v>0</v>
-      </c>
-      <c r="N8" s="4">
-        <v>0</v>
-      </c>
-      <c r="O8" s="4">
-        <v>0</v>
-      </c>
-      <c r="P8" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="4">
-        <v>0</v>
-      </c>
-      <c r="R8" s="4">
-        <v>0</v>
-      </c>
-      <c r="S8" s="4">
-        <v>0</v>
-      </c>
-      <c r="T8" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
-      <c r="A9" s="4">
+      <c r="D8" s="3">
+        <v>0</v>
+      </c>
+      <c r="E8" s="6">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3">
+        <v>0</v>
+      </c>
+      <c r="K8" s="3">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3">
+        <v>0</v>
+      </c>
+      <c r="N8" s="3">
+        <v>0</v>
+      </c>
+      <c r="O8" s="3">
+        <v>0</v>
+      </c>
+      <c r="P8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+      <c r="R8" s="3">
+        <v>0</v>
+      </c>
+      <c r="S8" s="3">
+        <v>0</v>
+      </c>
+      <c r="T8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
+      <c r="A9" s="3">
         <v>11</v>
       </c>
-      <c r="B9" s="4">
-        <v>1</v>
-      </c>
-      <c r="C9" s="3">
+      <c r="B9" s="3">
+        <v>1</v>
+      </c>
+      <c r="C9" s="2">
         <v>1.55608</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="3">
         <v>553</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="6">
         <v>16.621136287753217</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="2">
         <v>1.7</v>
       </c>
-      <c r="G9" s="4">
-        <v>0</v>
-      </c>
-      <c r="H9" s="4">
-        <v>1</v>
-      </c>
-      <c r="I9" s="4">
-        <v>0</v>
-      </c>
-      <c r="J9" s="3">
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3">
+        <v>1</v>
+      </c>
+      <c r="I9" s="3">
+        <v>0</v>
+      </c>
+      <c r="J9" s="2">
         <v>0.02094228464</v>
       </c>
-      <c r="K9" s="4">
+      <c r="K9" s="3">
         <v>180</v>
       </c>
-      <c r="L9" s="4">
-        <v>0</v>
-      </c>
-      <c r="M9" s="4">
-        <v>0</v>
-      </c>
-      <c r="N9" s="4">
-        <v>0</v>
-      </c>
-      <c r="O9" s="4">
-        <v>0</v>
-      </c>
-      <c r="P9" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="4">
-        <v>0</v>
-      </c>
-      <c r="R9" s="4">
-        <v>0</v>
-      </c>
-      <c r="S9" s="4">
-        <v>0</v>
-      </c>
-      <c r="T9" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
-      <c r="A10" s="4">
+      <c r="L9" s="3">
+        <v>0</v>
+      </c>
+      <c r="M9" s="3">
+        <v>0</v>
+      </c>
+      <c r="N9" s="3">
+        <v>0</v>
+      </c>
+      <c r="O9" s="3">
+        <v>0</v>
+      </c>
+      <c r="P9" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>0</v>
+      </c>
+      <c r="R9" s="3">
+        <v>0</v>
+      </c>
+      <c r="S9" s="3">
+        <v>0</v>
+      </c>
+      <c r="T9" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
+      <c r="A10" s="3">
         <v>12</v>
       </c>
-      <c r="B10" s="4">
-        <v>1</v>
-      </c>
-      <c r="C10" s="3">
+      <c r="B10" s="3">
+        <v>1</v>
+      </c>
+      <c r="C10" s="2">
         <v>1.55608</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="3">
         <v>553</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="6">
         <v>16.621136287753217</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="2">
         <v>1.7</v>
       </c>
-      <c r="G10" s="4">
-        <v>0</v>
-      </c>
-      <c r="H10" s="4">
-        <v>1</v>
-      </c>
-      <c r="I10" s="4">
-        <v>0</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3">
+        <v>1</v>
+      </c>
+      <c r="I10" s="3">
+        <v>0</v>
+      </c>
+      <c r="J10" s="2">
         <v>0.02094228464</v>
       </c>
-      <c r="K10" s="4">
+      <c r="K10" s="3">
         <v>180</v>
       </c>
-      <c r="L10" s="4">
-        <v>0</v>
-      </c>
-      <c r="M10" s="4">
-        <v>0</v>
-      </c>
-      <c r="N10" s="4">
-        <v>0</v>
-      </c>
-      <c r="O10" s="4">
-        <v>0</v>
-      </c>
-      <c r="P10" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="4">
-        <v>0</v>
-      </c>
-      <c r="R10" s="4">
-        <v>0</v>
-      </c>
-      <c r="S10" s="4">
-        <v>0</v>
-      </c>
-      <c r="T10" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
-      <c r="A11" s="4">
+      <c r="L10" s="3">
+        <v>0</v>
+      </c>
+      <c r="M10" s="3">
+        <v>0</v>
+      </c>
+      <c r="N10" s="3">
+        <v>0</v>
+      </c>
+      <c r="O10" s="3">
+        <v>0</v>
+      </c>
+      <c r="P10" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>0</v>
+      </c>
+      <c r="R10" s="3">
+        <v>0</v>
+      </c>
+      <c r="S10" s="3">
+        <v>0</v>
+      </c>
+      <c r="T10" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
+      <c r="A11" s="3">
         <v>13</v>
       </c>
-      <c r="B11" s="4">
-        <v>1</v>
-      </c>
-      <c r="C11" s="3">
+      <c r="B11" s="3">
+        <v>1</v>
+      </c>
+      <c r="C11" s="2">
         <v>1.55608</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="3">
         <v>553</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="6">
         <v>16.621136287753217</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="2">
         <v>1.7</v>
       </c>
-      <c r="G11" s="4">
-        <v>0</v>
-      </c>
-      <c r="H11" s="4">
-        <v>1</v>
-      </c>
-      <c r="I11" s="4">
-        <v>0</v>
-      </c>
-      <c r="J11" s="3">
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="3">
+        <v>1</v>
+      </c>
+      <c r="I11" s="3">
+        <v>0</v>
+      </c>
+      <c r="J11" s="2">
         <v>0.02094228464</v>
       </c>
-      <c r="K11" s="4">
+      <c r="K11" s="3">
         <v>180</v>
       </c>
-      <c r="L11" s="4">
-        <v>0</v>
-      </c>
-      <c r="M11" s="4">
-        <v>0</v>
-      </c>
-      <c r="N11" s="4">
-        <v>0</v>
-      </c>
-      <c r="O11" s="4">
-        <v>0</v>
-      </c>
-      <c r="P11" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="4">
-        <v>0</v>
-      </c>
-      <c r="R11" s="4">
-        <v>0</v>
-      </c>
-      <c r="S11" s="4">
-        <v>0</v>
-      </c>
-      <c r="T11" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
-      <c r="A12" s="4">
+      <c r="L11" s="3">
+        <v>0</v>
+      </c>
+      <c r="M11" s="3">
+        <v>0</v>
+      </c>
+      <c r="N11" s="3">
+        <v>0</v>
+      </c>
+      <c r="O11" s="3">
+        <v>0</v>
+      </c>
+      <c r="P11" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>0</v>
+      </c>
+      <c r="R11" s="3">
+        <v>0</v>
+      </c>
+      <c r="S11" s="3">
+        <v>0</v>
+      </c>
+      <c r="T11" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
+      <c r="A12" s="3">
         <v>14</v>
       </c>
-      <c r="B12" s="4">
-        <v>1</v>
-      </c>
-      <c r="C12" s="3">
+      <c r="B12" s="3">
+        <v>1</v>
+      </c>
+      <c r="C12" s="2">
         <v>1.55608</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="3">
         <v>553</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E12" s="6">
         <v>16.621136287753217</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="2">
         <v>1.7</v>
       </c>
-      <c r="G12" s="4">
-        <v>0</v>
-      </c>
-      <c r="H12" s="4">
-        <v>1</v>
-      </c>
-      <c r="I12" s="4">
-        <v>0</v>
-      </c>
-      <c r="J12" s="3">
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="3">
+        <v>1</v>
+      </c>
+      <c r="I12" s="3">
+        <v>0</v>
+      </c>
+      <c r="J12" s="2">
         <v>0.02094228464</v>
       </c>
-      <c r="K12" s="4">
+      <c r="K12" s="3">
         <v>180</v>
       </c>
-      <c r="L12" s="4">
-        <v>0</v>
-      </c>
-      <c r="M12" s="4">
-        <v>0</v>
-      </c>
-      <c r="N12" s="4">
-        <v>0</v>
-      </c>
-      <c r="O12" s="4">
-        <v>0</v>
-      </c>
-      <c r="P12" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="4">
-        <v>0</v>
-      </c>
-      <c r="R12" s="4">
-        <v>0</v>
-      </c>
-      <c r="S12" s="4">
-        <v>0</v>
-      </c>
-      <c r="T12" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
-      <c r="A13" s="4">
+      <c r="L12" s="3">
+        <v>0</v>
+      </c>
+      <c r="M12" s="3">
+        <v>0</v>
+      </c>
+      <c r="N12" s="3">
+        <v>0</v>
+      </c>
+      <c r="O12" s="3">
+        <v>0</v>
+      </c>
+      <c r="P12" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>0</v>
+      </c>
+      <c r="R12" s="3">
+        <v>0</v>
+      </c>
+      <c r="S12" s="3">
+        <v>0</v>
+      </c>
+      <c r="T12" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
+      <c r="A13" s="3">
         <v>15</v>
       </c>
-      <c r="B13" s="4">
-        <v>1</v>
-      </c>
-      <c r="C13" s="3">
+      <c r="B13" s="3">
+        <v>1</v>
+      </c>
+      <c r="C13" s="2">
         <v>1.55608</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="3">
         <v>553</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="6">
         <v>16.621136287753217</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="2">
         <v>1.7</v>
       </c>
-      <c r="G13" s="4">
-        <v>0</v>
-      </c>
-      <c r="H13" s="4">
-        <v>1</v>
-      </c>
-      <c r="I13" s="4">
-        <v>0</v>
-      </c>
-      <c r="J13" s="3">
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="3">
+        <v>1</v>
+      </c>
+      <c r="I13" s="3">
+        <v>0</v>
+      </c>
+      <c r="J13" s="2">
         <v>0.02094228464</v>
       </c>
-      <c r="K13" s="4">
+      <c r="K13" s="3">
         <v>180</v>
       </c>
-      <c r="L13" s="4">
-        <v>0</v>
-      </c>
-      <c r="M13" s="4">
-        <v>0</v>
-      </c>
-      <c r="N13" s="4">
-        <v>0</v>
-      </c>
-      <c r="O13" s="4">
-        <v>0</v>
-      </c>
-      <c r="P13" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="4">
-        <v>0</v>
-      </c>
-      <c r="R13" s="4">
-        <v>0</v>
-      </c>
-      <c r="S13" s="4">
-        <v>0</v>
-      </c>
-      <c r="T13" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
-      <c r="A14" s="4">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
+      <c r="A14" s="3">
         <v>16</v>
       </c>
-      <c r="B14" s="4">
-        <v>1</v>
-      </c>
-      <c r="C14" s="3">
+      <c r="B14" s="3">
+        <v>1</v>
+      </c>
+      <c r="C14" s="2">
         <v>1.55608</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14" s="3">
         <v>553</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E14" s="6">
         <v>16.621136287753217</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="2">
         <v>1.7</v>
       </c>
-      <c r="G14" s="4">
-        <v>0</v>
-      </c>
-      <c r="H14" s="4">
-        <v>1</v>
-      </c>
-      <c r="I14" s="4">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
+        <v>1</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="2">
         <v>0.02094228464</v>
       </c>
-      <c r="K14" s="4">
+      <c r="K14" s="3">
         <v>180</v>
       </c>
-      <c r="L14" s="4">
-        <v>0</v>
-      </c>
-      <c r="M14" s="4">
-        <v>0</v>
-      </c>
-      <c r="N14" s="4">
-        <v>0</v>
-      </c>
-      <c r="O14" s="4">
-        <v>0</v>
-      </c>
-      <c r="P14" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="4">
-        <v>0</v>
-      </c>
-      <c r="R14" s="4">
-        <v>0</v>
-      </c>
-      <c r="S14" s="4">
-        <v>0</v>
-      </c>
-      <c r="T14" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
-      <c r="A15" s="4">
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
+      <c r="A15" s="3">
         <v>20</v>
       </c>
-      <c r="B15" s="4">
-        <v>1</v>
-      </c>
-      <c r="C15" s="4">
-        <v>0</v>
-      </c>
-      <c r="D15" s="4">
-        <v>0</v>
-      </c>
-      <c r="E15" s="9">
-        <v>0</v>
-      </c>
-      <c r="F15" s="4">
-        <v>0</v>
-      </c>
-      <c r="G15" s="4">
-        <v>0</v>
-      </c>
-      <c r="H15" s="4">
-        <v>0</v>
-      </c>
-      <c r="I15" s="4">
-        <v>0</v>
-      </c>
-      <c r="J15" s="4">
-        <v>0</v>
-      </c>
-      <c r="K15" s="4">
-        <v>0</v>
-      </c>
-      <c r="L15" s="4">
-        <v>0</v>
-      </c>
-      <c r="M15" s="4">
-        <v>0</v>
-      </c>
-      <c r="N15" s="4">
-        <v>0</v>
-      </c>
-      <c r="O15" s="4">
-        <v>0</v>
-      </c>
-      <c r="P15" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="4">
-        <v>0</v>
-      </c>
-      <c r="R15" s="4">
-        <v>0</v>
-      </c>
-      <c r="S15" s="4">
-        <v>0</v>
-      </c>
-      <c r="T15" s="4">
+      <c r="B15" s="3">
+        <v>1</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="6">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3">
+        <v>0</v>
+      </c>
+      <c r="K15" s="3">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+      <c r="T15" s="3">
         <v>0</v>
       </c>
     </row>
@@ -2040,8 +2031,8 @@
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -2072,7 +2063,7 @@
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="2">
         <v>0.000001</v>
       </c>
     </row>
@@ -2080,7 +2071,7 @@
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="3">
         <v>100</v>
       </c>
     </row>
@@ -2088,7 +2079,7 @@
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="2">
         <v>1e-10</v>
       </c>
     </row>
